--- a/data/trans_orig/P79_n_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R2-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>498292</t>
+          <t>541769</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492222</t>
+          <t>533179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502309</t>
+          <t>546377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>442441</t>
+          <t>482062</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>437943</t>
+          <t>475951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>445468</t>
+          <t>485416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>940733</t>
+          <t>1023831</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>932221</t>
+          <t>1014811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>945770</t>
+          <t>1030213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>443448</t>
+          <t>473791</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435446</t>
+          <t>466163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447913</t>
+          <t>478928</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>376126</t>
+          <t>416101</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371359</t>
+          <t>409747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379521</t>
+          <t>419621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>819574</t>
+          <t>889892</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810557</t>
+          <t>881960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>825928</t>
+          <t>896771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>29420</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>20579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>642694</t>
+          <t>442192</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621532</t>
+          <t>430221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659711</t>
+          <t>451033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>163440</t>
+          <t>183118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159498</t>
+          <t>178792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165323</t>
+          <t>185711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>806133</t>
+          <t>625309</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789528</t>
+          <t>613496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823298</t>
+          <t>635315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45981</t>
+          <t>53028</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>40296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63828</t>
+          <t>71047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30294</t>
+          <t>32163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65385</t>
+          <t>74853</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45733</t>
+          <t>57479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85363</t>
+          <t>95468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>988838</t>
+          <t>1078815</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>970991</t>
+          <t>1060796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1001178</t>
+          <t>1091547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>958690</t>
+          <t>839386</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947800</t>
+          <t>829048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>967851</t>
+          <t>845959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1947527</t>
+          <t>1918201</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1927549</t>
+          <t>1897586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967179</t>
+          <t>1935575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41314</t>
+          <t>46309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>62175</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>76713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>78897</t>
+          <t>95256</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58888</t>
+          <t>78036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98242</t>
+          <t>114097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>445818</t>
+          <t>534883</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>433732</t>
+          <t>521655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455987</t>
+          <t>545325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>791667</t>
+          <t>768675</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>776749</t>
+          <t>754137</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>806234</t>
+          <t>783143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1237484</t>
+          <t>1303558</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1218139</t>
+          <t>1284717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257493</t>
+          <t>1320778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43908</t>
+          <t>47025</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31924</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60624</t>
+          <t>61695</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>54408</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>41770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67508</t>
+          <t>72589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235525</t>
+          <t>229845</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226988</t>
+          <t>220078</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239189</t>
+          <t>235316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>717463</t>
+          <t>797256</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>700747</t>
+          <t>782586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>729447</t>
+          <t>808918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>952988</t>
+          <t>1027101</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>934370</t>
+          <t>1008920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>966219</t>
+          <t>1039739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>121447</t>
+          <t>141182</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94948</t>
+          <t>116576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149754</t>
+          <t>166321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>127930</t>
+          <t>148795</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102037</t>
+          <t>125823</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154268</t>
+          <t>172804</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>249377</t>
+          <t>289978</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>209392</t>
+          <t>259040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>287950</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3254613</t>
+          <t>3301294</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3226306</t>
+          <t>3276155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3281112</t>
+          <t>3325900</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3449828</t>
+          <t>3486598</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3423490</t>
+          <t>3462589</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3475721</t>
+          <t>3509570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6704441</t>
+          <t>6787891</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6665868</t>
+          <t>6753385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6744426</t>
+          <t>6818829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
